--- a/data/file_generation/input/data_73/员工绩效.xlsx
+++ b/data/file_generation/input/data_73/员工绩效.xlsx
@@ -1942,26 +1942,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{805BE93E-1192-4C4C-BB65-83B27D5B5DF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCDC3583-6DBE-4159-B0F7-B4B3E598D0B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D875B-DD38-4367-B2D4-33D3C2840A6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB748C2-A3F4-4527-B531-CDE49624D30E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{912B3BA0-AF4E-4989-BBC4-773665194360}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F919183-31C9-4E21-BBC4-BF8DF3CA00B2}"/>
 </file>